--- a/Stibo STEP Global Business Rules v1.3.with-detail.xlsx
+++ b/Stibo STEP Global Business Rules v1.3.with-detail.xlsx
@@ -157,7 +157,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -335,13 +335,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -409,6 +418,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -31643,6 +31654,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t>approves items</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>Actions</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="409.5" customHeight="1">
       <c r="A201" t="n">
@@ -31877,6 +31898,21 @@
 // ... truncated ...</t>
         </is>
       </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>Error: Please select only one History object at a time.</t>
+        </is>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>looks up related records; creates/updates references, shows user alert</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>Actions</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="341" customHeight="1">
       <c r="A202" t="n">
@@ -31947,6 +31983,21 @@
 }</t>
         </is>
       </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>ERROR: Please set Soft Delete as 'No' to approve Revival!</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>Actions</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="341" customHeight="1">
       <c r="A203" t="n">
@@ -32015,6 +32066,21 @@
 	}
 }
 }</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>ERROR: Please set Soft Delete as 'Yes' to approve Soft Delete</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>Actions</t>
         </is>
       </c>
     </row>
@@ -32089,6 +32155,16 @@
 	}
 }
 }</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>looks up related records; approves items</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>Actions</t>
         </is>
       </c>
     </row>
@@ -32205,6 +32281,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>creates/updates references, updates attributes</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>Actions</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="409.5" customHeight="1">
       <c r="A206" t="n">
@@ -32381,6 +32467,21 @@
 */</t>
         </is>
       </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>Error: Duplicate Email ID found : | ACKNOWLEDGEMENT: Success Message | is missing. Please provide a value.</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>updates attributes, shows user alert</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>Actions</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="409.5" customHeight="1">
       <c r="A207" t="n">
@@ -32453,6 +32554,21 @@
   "pluginType" : "Precondition"
 }
 */</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>ACKNOWLEDGEMENT: Success Message</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>Actions</t>
         </is>
       </c>
     </row>
@@ -32546,6 +32662,21 @@
  	webUI.showAlert("ERROR",errorMsg);
  }
 }</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>ERROR | WARNING: &lt;br/&gt; | INFO</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>Actions</t>
         </is>
       </c>
     </row>
@@ -32618,6 +32749,21 @@
 }</t>
         </is>
       </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>ERROR: Please set Soft Delete as 'Yes' to reject Revival!</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>Actions</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="341" customHeight="1">
       <c r="A210" t="n">
@@ -32686,6 +32832,21 @@
 	}
 }
 }</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>ERROR: Please set Soft Delete as 'No' to reject Soft Delete!</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>Actions</t>
         </is>
       </c>
     </row>
@@ -32801,6 +32962,21 @@
 }</t>
         </is>
       </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>Actions</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="409.5" customHeight="1">
       <c r="A212" t="n">
@@ -32896,6 +33072,21 @@
  	webUI.showAlert("ERROR",errorMsg);
  }
 }</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>ERROR | WARNING: &lt;br/&gt; | INFO</t>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>Actions</t>
         </is>
       </c>
     </row>
@@ -33006,6 +33197,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>Actions</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="409.5" customHeight="1">
       <c r="A214" t="n">
@@ -33108,6 +33309,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>Actions</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="139.5" customHeight="1">
       <c r="A215" t="n">
@@ -33163,6 +33374,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>getDataContainerByTypeID(), deleteLocal()</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>Actions</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="124" customHeight="1">
       <c r="A216" t="n">
@@ -33210,6 +33431,16 @@
 exports.operation0 = function (node,refObj,stepMan) {
 var returnClassInfo = node.createClassificationProductLink(stepMan.getClassificationHome().getClassificationByID("SC_" + ID), refObj);
 }</t>
+        </is>
+      </c>
+      <c r="AD216" t="inlineStr">
+        <is>
+          <t>creates related objects</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>Actions</t>
         </is>
       </c>
     </row>
@@ -33266,6 +33497,16 @@
 node.getValue("ISMNIPTYPE").setSimpleValue('Z3');
 node.getValue("ISMPERRULE").setSimpleValue('MONTH');
 }</t>
+        </is>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>Actions</t>
         </is>
       </c>
     </row>
@@ -33352,6 +33593,21 @@
 	}
 }
 }</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>GenericFunctions (genericFunctions)</t>
+        </is>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>Actions</t>
         </is>
       </c>
     </row>
@@ -33551,6 +33807,21 @@
 }</t>
         </is>
       </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>GenericFunctions (genericFunctions)</t>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>approves items, creates related objects</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>AutoClassifyRules</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="409.5" customHeight="1">
       <c r="A220" t="n">
@@ -33632,6 +33903,16 @@
 		node.setParent(parentObject);
 }
 }</t>
+        </is>
+      </c>
+      <c r="AD220" t="inlineStr">
+        <is>
+          <t>setParent(), getProductByID()</t>
+        </is>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>AutoClassifyRules</t>
         </is>
       </c>
     </row>
@@ -33742,6 +34023,16 @@
 	NODE.setParent(parentObject);
 } 
 }</t>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>AutoClassifyRules</t>
         </is>
       </c>
     </row>
@@ -33997,6 +34288,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue(), setParent(), getParent(), getProductByID()</t>
+        </is>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>AutoClassifyRules</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="409.5" customHeight="1">
       <c r="A223" t="n">
@@ -34074,6 +34375,16 @@
 	return false;
 }
 }</t>
+        </is>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>BackfilesUpsertGroup</t>
         </is>
       </c>
     </row>
@@ -34143,6 +34454,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>BackfilesUpsertGroup</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="372" customHeight="1">
       <c r="A225" t="n">
@@ -34212,6 +34533,21 @@
 UI.showAlert("ACKNOWLEDGMENT", "Backfile successfully saved!");
 }
 }</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>WARNING | ACKNOWLEDGMENT</t>
+        </is>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>updates attributes, shows user alert</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>BackfilesUpsertGroup</t>
         </is>
       </c>
     </row>
@@ -34322,6 +34658,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>CollectionGroup</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="62" customHeight="1">
       <c r="A227" t="n">
@@ -34367,6 +34713,16 @@
           <t xml:space="preserve">File: Conditions/BC_CheckManualAGA.js
 Plugin: AttributeComparatorCondition
 </t>
+        </is>
+      </c>
+      <c r="AD227" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>Conditions</t>
         </is>
       </c>
     </row>
@@ -34445,6 +34801,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="62" customHeight="1">
       <c r="A229" t="n">
@@ -34490,6 +34856,16 @@
           <t xml:space="preserve">File: Conditions/BC_FalseForSoftDelete.js
 Plugin: AttributeComparatorCondition
 </t>
+        </is>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>Conditions</t>
         </is>
       </c>
     </row>
@@ -34571,6 +34947,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t>getChildren()</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="217" customHeight="1">
       <c r="A231" t="n">
@@ -34627,6 +35013,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>getParent()</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="62" customHeight="1">
       <c r="A232" t="n">
@@ -34672,6 +35068,16 @@
           <t xml:space="preserve">File: Conditions/BC_TrueForSoftDelete.js
 Plugin: AttributeComparatorCondition
 </t>
+        </is>
+      </c>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>Conditions</t>
         </is>
       </c>
     </row>
@@ -34880,6 +35286,21 @@
 }</t>
         </is>
       </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>GenericFunctions (genericFunctions)</t>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue(), getDataContainerObjects()</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="409.5" customHeight="1">
       <c r="A234" t="n">
@@ -35000,6 +35421,21 @@
 }</t>
         </is>
       </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>GenericFunctions (genericFunctions)</t>
+        </is>
+      </c>
+      <c r="AD234" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue(), getDataContainerObjects()</t>
+        </is>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="232.5" customHeight="1">
       <c r="A235" t="n">
@@ -35058,6 +35494,16 @@
 	return false;
 }
 }</t>
+        </is>
+      </c>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>Conditions</t>
         </is>
       </c>
     </row>
@@ -35139,6 +35585,21 @@
 }</t>
         </is>
       </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>GenericFunctions (genericFunctions)</t>
+        </is>
+      </c>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue(), getDataContainerObjects()</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="409.5" customHeight="1">
       <c r="A237" t="n">
@@ -35208,6 +35669,26 @@
 	UI.showAlert("ERROR", "Value Pair of Bundle Code, Bundle Group, and Subscription Type is duplicated, please fix.");
 }
 }</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>ERROR: Value Pair of Bundle Code, Bundle Group, and Subscription Type is duplicated, please fix.</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>GenericFunctions (genericFunctions)</t>
+        </is>
+      </c>
+      <c r="AD237" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE237" t="inlineStr">
+        <is>
+          <t>Conditions</t>
         </is>
       </c>
     </row>
@@ -35348,6 +35829,16 @@
 */</t>
         </is>
       </c>
+      <c r="AD238" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="409.5" customHeight="1">
       <c r="A239" t="n">
@@ -35769,6 +36260,16 @@
 */</t>
         </is>
       </c>
+      <c r="AD239" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="356.5" customHeight="1">
       <c r="A240" t="n">
@@ -35831,6 +36332,16 @@
 }
 }
 }</t>
+        </is>
+      </c>
+      <c r="AD240" t="inlineStr">
+        <is>
+          <t>looks up related records</t>
+        </is>
+      </c>
+      <c r="AE240" t="inlineStr">
+        <is>
+          <t>Conditions</t>
         </is>
       </c>
     </row>
@@ -35975,6 +36486,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD241" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="294.5" customHeight="1">
       <c r="A242" t="n">
@@ -36040,6 +36561,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="201.5" customHeight="1">
       <c r="A243" t="n">
@@ -36097,6 +36628,16 @@
 }
 return true;
 }</t>
+        </is>
+      </c>
+      <c r="AD243" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t>Conditions</t>
         </is>
       </c>
     </row>
@@ -36158,6 +36699,16 @@
 	return false;
 }
 }</t>
+        </is>
+      </c>
+      <c r="AD244" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>Conditions</t>
         </is>
       </c>
     </row>
@@ -36311,6 +36862,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue(), getChildren(), getParent()</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="409.5" customHeight="1">
       <c r="A246" t="n">
@@ -36379,6 +36940,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>getChildren(), getParent()</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="279" customHeight="1">
       <c r="A247" t="n">
@@ -36438,6 +37009,16 @@
   "pluginType" : "Operation"
 }
 */</t>
+        </is>
+      </c>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>Conditions</t>
         </is>
       </c>
     </row>
@@ -36514,6 +37095,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue(), getParent()</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="232.5" customHeight="1">
       <c r="A249" t="n">
@@ -36574,6 +37165,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue(), getParent()</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="201.5" customHeight="1">
       <c r="A250" t="n">
@@ -36633,6 +37234,21 @@
 }</t>
         </is>
       </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>ACKNOWLEDGMENT</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="139.5" customHeight="1">
       <c r="A251" t="n">
@@ -36685,6 +37301,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>getValue()</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="139.5" customHeight="1">
       <c r="A252" t="n">
@@ -36735,6 +37361,16 @@
 }
 return false;
 }</t>
+        </is>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>getValue()</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>Conditions</t>
         </is>
       </c>
     </row>
@@ -36801,6 +37437,16 @@
 	}
 return false;
 }</t>
+        </is>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>Conditions</t>
         </is>
       </c>
     </row>
@@ -36877,6 +37523,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue(), getParent()</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="232.5" customHeight="1">
       <c r="A255" t="n">
@@ -36937,6 +37593,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue(), getParent()</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="139.5" customHeight="1">
       <c r="A256" t="n">
@@ -36994,6 +37660,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="139.5" customHeight="1">
       <c r="A257" t="n">
@@ -37044,6 +37720,16 @@
 }
 return true;
 }</t>
+        </is>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>Conditions</t>
         </is>
       </c>
     </row>
@@ -37103,6 +37789,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="232.5" customHeight="1">
       <c r="A259" t="n">
@@ -37160,6 +37856,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD259" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE259" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="155" customHeight="1">
       <c r="A260" t="n">
@@ -37217,6 +37923,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD260" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE260" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="139.5" customHeight="1">
       <c r="A261" t="n">
@@ -37274,6 +37990,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD261" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="155" customHeight="1">
       <c r="A262" t="n">
@@ -37331,6 +38057,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD262" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="155" customHeight="1">
       <c r="A263" t="n">
@@ -37388,6 +38124,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD263" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="155" customHeight="1">
       <c r="A264" t="n">
@@ -37443,6 +38189,16 @@
 }
 return true;
 }</t>
+        </is>
+      </c>
+      <c r="AD264" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>Conditions</t>
         </is>
       </c>
     </row>
@@ -37515,6 +38271,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD265" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="155" customHeight="1">
       <c r="A266" t="n">
@@ -37572,6 +38338,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD266" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="139.5" customHeight="1">
       <c r="A267" t="n">
@@ -37629,6 +38405,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD267" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="170.5" customHeight="1">
       <c r="A268" t="n">
@@ -37686,6 +38472,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD268" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE268" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="139.5" customHeight="1">
       <c r="A269" t="n">
@@ -37743,6 +38539,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD269" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="139.5" customHeight="1">
       <c r="A270" t="n">
@@ -37800,6 +38606,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD270" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="155" customHeight="1">
       <c r="A271" t="n">
@@ -37857,6 +38673,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD271" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="155" customHeight="1">
       <c r="A272" t="n">
@@ -37914,6 +38740,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD272" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="139.5" customHeight="1">
       <c r="A273" t="n">
@@ -37971,6 +38807,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="155" customHeight="1">
       <c r="A274" t="n">
@@ -38028,6 +38874,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD274" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="217" customHeight="1">
       <c r="A275" t="n">
@@ -38083,6 +38939,16 @@
 }
 return false;
 }</t>
+        </is>
+      </c>
+      <c r="AD275" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>Conditions</t>
         </is>
       </c>
     </row>
@@ -38143,6 +39009,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD276" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="139.5" customHeight="1">
       <c r="A277" t="n">
@@ -38198,6 +39074,16 @@
 }
 return false;
 }</t>
+        </is>
+      </c>
+      <c r="AD277" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>Conditions</t>
         </is>
       </c>
     </row>
@@ -38264,6 +39150,16 @@
 }
 return false;
 }</t>
+        </is>
+      </c>
+      <c r="AD278" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE278" t="inlineStr">
+        <is>
+          <t>Conditions</t>
         </is>
       </c>
     </row>
@@ -38440,6 +39336,21 @@
 }</t>
         </is>
       </c>
+      <c r="AC279" t="inlineStr">
+        <is>
+          <t>GenericFunctions (genericFunctions)</t>
+        </is>
+      </c>
+      <c r="AD279" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue(), getDataContainerObjects()</t>
+        </is>
+      </c>
+      <c r="AE279" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="403" customHeight="1">
       <c r="A280" t="n">
@@ -38498,6 +39409,16 @@
 }
 return isReadOnly;
 }</t>
+        </is>
+      </c>
+      <c r="AD280" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE280" t="inlineStr">
+        <is>
+          <t>Conditions</t>
         </is>
       </c>
     </row>
@@ -38575,6 +39496,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD281" t="inlineStr">
+        <is>
+          <t>asList()</t>
+        </is>
+      </c>
+      <c r="AE281" t="inlineStr">
+        <is>
+          <t>Functions</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="409.5" customHeight="1">
       <c r="A282" t="n">
@@ -38648,6 +39579,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD282" t="inlineStr">
+        <is>
+          <t>getProductByID(), asList()</t>
+        </is>
+      </c>
+      <c r="AE282" t="inlineStr">
+        <is>
+          <t>Functions</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="62" customHeight="1">
       <c r="A283" t="n">
@@ -38693,6 +39634,16 @@
           <t xml:space="preserve">File: Functions/BF_TargetSearchFunctionForHistoryParent.js
 Plugin: QueryBusinessFunction
 </t>
+        </is>
+      </c>
+      <c r="AD283" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE283" t="inlineStr">
+        <is>
+          <t>Functions</t>
         </is>
       </c>
     </row>
@@ -38768,6 +39719,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD284" t="inlineStr">
+        <is>
+          <t>getProductByID(), asList()</t>
+        </is>
+      </c>
+      <c r="AE284" t="inlineStr">
+        <is>
+          <t>Functions</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="108.5" customHeight="1">
       <c r="A285" t="n">
@@ -38818,6 +39779,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD285" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE285" t="inlineStr">
+        <is>
+          <t>Functions</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="108.5" customHeight="1">
       <c r="A286" t="n">
@@ -38868,6 +39839,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD286" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE286" t="inlineStr">
+        <is>
+          <t>Functions</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="108.5" customHeight="1">
       <c r="A287" t="n">
@@ -38917,6 +39898,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD287" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE287" t="inlineStr">
+        <is>
+          <t>Functions</t>
+        </is>
+      </c>
     </row>
     <row r="288" ht="62" customHeight="1">
       <c r="A288" t="n">
@@ -38957,6 +39948,16 @@
           <t xml:space="preserve">File: Functions/prodIdentifierQuery.js
 Plugin: 
 </t>
+        </is>
+      </c>
+      <c r="AD288" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE288" t="inlineStr">
+        <is>
+          <t>Functions</t>
         </is>
       </c>
     </row>
@@ -39107,6 +40108,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD289" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE289" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
     </row>
     <row r="290" ht="409.5" customHeight="1">
       <c r="A290" t="n">
@@ -39261,6 +40272,21 @@
 	return dateTime;
 }
 }</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>No SAP Number found for Issue object with SAP Materail Number:</t>
+        </is>
+      </c>
+      <c r="AD290" t="inlineStr">
+        <is>
+          <t>approves items, creates/updates references, updates attributes, creates related objects</t>
+        </is>
+      </c>
+      <c r="AE290" t="inlineStr">
+        <is>
+          <t>Integrations</t>
         </is>
       </c>
     </row>
@@ -39497,6 +40523,21 @@
 // ... truncated ...</t>
         </is>
       </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>Invalid inbound JPCMS ID: | Invalid inbound JPCMS Dates to Check: | Multiple Journal matches found | No Issue was found with that volume and issue number | No Journals match</t>
+        </is>
+      </c>
+      <c r="AD291" t="inlineStr">
+        <is>
+          <t>creates/updates references, updates attributes, creates related objects</t>
+        </is>
+      </c>
+      <c r="AE291" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="409.5" customHeight="1">
       <c r="A292" t="n">
@@ -39750,6 +40791,21 @@
 // ... truncated ...</t>
         </is>
       </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>Multiple Issues matches found for DOI | Multiple Journal Media matches found for eISSN | Inbound WOL event unable to match a Volume and Issue in STEP | Inbound WOL event unable to match a volume and issue in STEP | Inbound WOL event unable to match a…</t>
+        </is>
+      </c>
+      <c r="AD292" t="inlineStr">
+        <is>
+          <t>creates/updates references, updates attributes, creates related objects</t>
+        </is>
+      </c>
+      <c r="AE292" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="409.5" customHeight="1">
       <c r="A293" t="n">
@@ -39867,6 +40923,21 @@
 }</t>
         </is>
       </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>No STEP ID found for object requested:</t>
+        </is>
+      </c>
+      <c r="AD293" t="inlineStr">
+        <is>
+          <t>approves items, updates attributes</t>
+        </is>
+      </c>
+      <c r="AE293" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
     </row>
     <row r="294" ht="325.5" customHeight="1">
       <c r="A294" t="n">
@@ -39931,6 +41002,16 @@
 	log.info('After setting value:'+object.getValue("SAP_Plants").getSimpleValue())
 }
 }</t>
+        </is>
+      </c>
+      <c r="AD294" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE294" t="inlineStr">
+        <is>
+          <t>Integrations</t>
         </is>
       </c>
     </row>
@@ -39998,6 +41079,16 @@
 log.info("formatteddate " + formatteddate)
 node.getValue("LastUpdatedNew").setSimpleValue(formatteddate);
 }</t>
+        </is>
+      </c>
+      <c r="AD295" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE295" t="inlineStr">
+        <is>
+          <t>Integrations</t>
         </is>
       </c>
     </row>
@@ -40252,6 +41343,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD296" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue(), getParent()</t>
+        </is>
+      </c>
+      <c r="AE296" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
     </row>
     <row r="297" ht="409.5" customHeight="1">
       <c r="A297" t="n">
@@ -40348,6 +41449,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD297" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE297" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
     </row>
     <row r="298" ht="139.5" customHeight="1">
       <c r="A298" t="n">
@@ -40402,6 +41513,16 @@
 log.info("Date:"+dateRaw.substring(0,10));
 node.getValue("PublicationDate").setSimpleValue(dateRaw.substring(0,10));
 }</t>
+        </is>
+      </c>
+      <c r="AD298" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE298" t="inlineStr">
+        <is>
+          <t>Integrations</t>
         </is>
       </c>
     </row>
@@ -40710,6 +41831,16 @@
   return attributeValue ? attributeValue + "" : "";
 }
 }</t>
+        </is>
+      </c>
+      <c r="AD299" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue(), getChildren(), getParent(), getDataContainerByTypeID(), getDataContainerObjects()</t>
+        </is>
+      </c>
+      <c r="AE299" t="inlineStr">
+        <is>
+          <t>Integrations</t>
         </is>
       </c>
     </row>
@@ -41028,6 +42159,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD300" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue(), getChildren(), getParent(), getDataContainerByTypeID(), getDataContainerObjects()</t>
+        </is>
+      </c>
+      <c r="AE300" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
     </row>
     <row r="301" ht="409.5" customHeight="1">
       <c r="A301" t="n">
@@ -41126,6 +42267,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD301" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE301" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
     </row>
     <row r="302" ht="409.5" customHeight="1">
       <c r="A302" t="n">
@@ -41203,6 +42354,16 @@
   }
 }
 }</t>
+        </is>
+      </c>
+      <c r="AD302" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE302" t="inlineStr">
+        <is>
+          <t>Integrations</t>
         </is>
       </c>
     </row>
@@ -41298,6 +42459,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD303" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE303" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
     </row>
     <row r="304" ht="409.5" customHeight="1">
       <c r="A304" t="n">
@@ -41376,6 +42547,16 @@
   }
 }
 }</t>
+        </is>
+      </c>
+      <c r="AD304" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE304" t="inlineStr">
+        <is>
+          <t>Integrations</t>
         </is>
       </c>
     </row>
@@ -41471,6 +42652,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD305" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE305" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
     </row>
     <row r="306" ht="409.5" customHeight="1">
       <c r="A306" t="n">
@@ -41549,6 +42740,16 @@
   }
 }
 }</t>
+        </is>
+      </c>
+      <c r="AD306" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE306" t="inlineStr">
+        <is>
+          <t>Integrations</t>
         </is>
       </c>
     </row>
@@ -41646,6 +42847,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD307" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE307" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
     </row>
     <row r="308" ht="409.5" customHeight="1">
       <c r="A308" t="n">
@@ -41723,6 +42934,16 @@
   }
 }
 }</t>
+        </is>
+      </c>
+      <c r="AD308" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE308" t="inlineStr">
+        <is>
+          <t>Integrations</t>
         </is>
       </c>
     </row>
@@ -41819,6 +43040,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD309" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue(), getParent()</t>
+        </is>
+      </c>
+      <c r="AE309" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
     </row>
     <row r="310" ht="263.5" customHeight="1">
       <c r="A310" t="n">
@@ -41875,6 +43106,16 @@
 //	return true;
 //}
 }</t>
+        </is>
+      </c>
+      <c r="AD310" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE310" t="inlineStr">
+        <is>
+          <t>Integrations</t>
         </is>
       </c>
     </row>
@@ -41957,6 +43198,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD311" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE311" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
     </row>
     <row r="312" ht="409.5" customHeight="1">
       <c r="A312" t="n">
@@ -42029,6 +43280,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD312" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE312" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
     </row>
     <row r="313" ht="409.5" customHeight="1">
       <c r="A313" t="n">
@@ -42119,6 +43380,16 @@
 	return childObjects;
 }
 }</t>
+        </is>
+      </c>
+      <c r="AD313" t="inlineStr">
+        <is>
+          <t>getChildren()</t>
+        </is>
+      </c>
+      <c r="AE313" t="inlineStr">
+        <is>
+          <t>Integrations</t>
         </is>
       </c>
     </row>
@@ -42218,6 +43489,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD314" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE314" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
     </row>
     <row r="315" ht="62" customHeight="1">
       <c r="A315" t="n">
@@ -42263,6 +43544,16 @@
           <t xml:space="preserve">File: Integrations/Should_NonJournal_Trigger_Outbound.js
 Plugin: 
 </t>
+        </is>
+      </c>
+      <c r="AD315" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE315" t="inlineStr">
+        <is>
+          <t>Integrations</t>
         </is>
       </c>
     </row>
@@ -42343,6 +43634,16 @@
 }
 */
 }</t>
+        </is>
+      </c>
+      <c r="AD316" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE316" t="inlineStr">
+        <is>
+          <t>Integrations</t>
         </is>
       </c>
     </row>
@@ -42544,6 +43845,21 @@
 */</t>
         </is>
       </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>ACKNOWLEDGMENT</t>
+        </is>
+      </c>
+      <c r="AD317" t="inlineStr">
+        <is>
+          <t>approves items, updates attributes, shows user alert</t>
+        </is>
+      </c>
+      <c r="AE317" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
     </row>
     <row r="318" ht="409.5" customHeight="1">
       <c r="A318" t="n">
@@ -42615,6 +43931,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD318" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE318" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
     </row>
     <row r="319" ht="409.5" customHeight="1">
       <c r="A319" t="n">
@@ -42704,6 +44030,16 @@
 	log.info("inside else")
 }
 }</t>
+        </is>
+      </c>
+      <c r="AD319" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE319" t="inlineStr">
+        <is>
+          <t>Integrations</t>
         </is>
       </c>
     </row>
@@ -42850,6 +44186,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD320" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue(), getChildren(), asList()</t>
+        </is>
+      </c>
+      <c r="AE320" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
     </row>
     <row r="321" ht="186" customHeight="1">
       <c r="A321" t="n">
@@ -42907,6 +44253,16 @@
 node.getValue("SchedulingMarginKeyforFloats").setSimpleValue('000');
 node.getValue("TransportationGroup").setSimpleValue('0001');
 }</t>
+        </is>
+      </c>
+      <c r="AD321" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE321" t="inlineStr">
+        <is>
+          <t>IssuesGroup</t>
         </is>
       </c>
     </row>
@@ -43114,6 +44470,21 @@
 // ... truncated ...</t>
         </is>
       </c>
+      <c r="AC322" t="inlineStr">
+        <is>
+          <t>IssueFunctions (issueLibrary)</t>
+        </is>
+      </c>
+      <c r="AD322" t="inlineStr">
+        <is>
+          <t>updates attributes, shows user alert</t>
+        </is>
+      </c>
+      <c r="AE322" t="inlineStr">
+        <is>
+          <t>IssuesGroup</t>
+        </is>
+      </c>
     </row>
     <row r="323" ht="409.5" customHeight="1">
       <c r="A323" t="n">
@@ -43209,6 +44580,21 @@
 }</t>
         </is>
       </c>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>GenericFunctions (genericFunctions), IssueFunctions (issueLibrary), VolumeFunctions (volumeLibrary)</t>
+        </is>
+      </c>
+      <c r="AD323" t="inlineStr">
+        <is>
+          <t>updates attributes, removes items from workflow, shows user alert</t>
+        </is>
+      </c>
+      <c r="AE323" t="inlineStr">
+        <is>
+          <t>IssuesGroup</t>
+        </is>
+      </c>
     </row>
     <row r="324" ht="409.5" customHeight="1">
       <c r="A324" t="n">
@@ -43283,6 +44669,21 @@
 }</t>
         </is>
       </c>
+      <c r="AC324" t="inlineStr">
+        <is>
+          <t>IssueFunctions (issueLibrary)</t>
+        </is>
+      </c>
+      <c r="AD324" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE324" t="inlineStr">
+        <is>
+          <t>IssuesGroup</t>
+        </is>
+      </c>
     </row>
     <row r="325" ht="62" customHeight="1">
       <c r="A325" t="n">
@@ -43328,6 +44729,16 @@
           <t xml:space="preserve">File: IssuesGroup/IssuesWorkFlowGroup/IssueWF_PullFromJPCMS.js
 Plugin: ReferenceOtherBABusinessAction
 </t>
+        </is>
+      </c>
+      <c r="AD325" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE325" t="inlineStr">
+        <is>
+          <t>IssuesGroup</t>
         </is>
       </c>
     </row>
@@ -43394,6 +44805,21 @@
 }
 UI.showAlert("ACKNOWLEDGEMENT","Resend Status","The following Issues have been SUCCESSFULLY resent to SAP : \n"+republished+"\n The following Issues HAVE NOT BEEN RESENT To SAP, because they are not active yet : \n"+notRepublished);
 }</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>ACKNOWLEDGEMENT: Resend Status</t>
+        </is>
+      </c>
+      <c r="AD326" t="inlineStr">
+        <is>
+          <t>approves items, shows user alert</t>
+        </is>
+      </c>
+      <c r="AE326" t="inlineStr">
+        <is>
+          <t>IssuesGroup</t>
         </is>
       </c>
     </row>
@@ -43473,6 +44899,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD327" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE327" t="inlineStr">
+        <is>
+          <t>JournalHistoryGroup</t>
+        </is>
+      </c>
     </row>
     <row r="328" ht="409.5" customHeight="1">
       <c r="A328" t="n">
@@ -43611,6 +45047,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD328" t="inlineStr">
+        <is>
+          <t>looks up related records; approves items, creates/updates references, updates attributes, creates related objects</t>
+        </is>
+      </c>
+      <c r="AE328" t="inlineStr">
+        <is>
+          <t>JournalHistoryGroup</t>
+        </is>
+      </c>
     </row>
     <row r="329" ht="372" customHeight="1">
       <c r="A329" t="n">
@@ -43681,6 +45127,21 @@
 }</t>
         </is>
       </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>WARNING | ACKNOWLEDGMENT</t>
+        </is>
+      </c>
+      <c r="AD329" t="inlineStr">
+        <is>
+          <t>updates attributes, shows user alert</t>
+        </is>
+      </c>
+      <c r="AE329" t="inlineStr">
+        <is>
+          <t>JournalHistoryGroup</t>
+        </is>
+      </c>
     </row>
     <row r="330" ht="372" customHeight="1">
       <c r="A330" t="n">
@@ -43751,6 +45212,21 @@
 }</t>
         </is>
       </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>WARNING | ACKNOWLEDGMENT</t>
+        </is>
+      </c>
+      <c r="AD330" t="inlineStr">
+        <is>
+          <t>updates attributes, shows user alert</t>
+        </is>
+      </c>
+      <c r="AE330" t="inlineStr">
+        <is>
+          <t>JournalHistoryGroup</t>
+        </is>
+      </c>
     </row>
     <row r="331" ht="341" customHeight="1">
       <c r="A331" t="n">
@@ -43812,6 +45288,21 @@
 	myChilds.get(i).getValue("ProductSAPMaterialNumber").setSimpleValue(journalGroupCode + journalMediaCode);
 }	
 }</t>
+        </is>
+      </c>
+      <c r="AC331" t="inlineStr">
+        <is>
+          <t>GenericFunctions (genericFunctions)</t>
+        </is>
+      </c>
+      <c r="AD331" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE331" t="inlineStr">
+        <is>
+          <t>JournalMediaGroup</t>
         </is>
       </c>
     </row>
@@ -43883,6 +45374,21 @@
 }</t>
         </is>
       </c>
+      <c r="AC332" t="inlineStr">
+        <is>
+          <t>GenericFunctions (genericFunctions)</t>
+        </is>
+      </c>
+      <c r="AD332" t="inlineStr">
+        <is>
+          <t>updates attributes, sends email notification</t>
+        </is>
+      </c>
+      <c r="AE332" t="inlineStr">
+        <is>
+          <t>JournalMediaGroup</t>
+        </is>
+      </c>
     </row>
     <row r="333" ht="409.5" customHeight="1">
       <c r="A333" t="n">
@@ -44015,6 +45521,16 @@
   "pluginType" : "Operation"
 }
 */</t>
+        </is>
+      </c>
+      <c r="AD333" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE333" t="inlineStr">
+        <is>
+          <t>JournalMediaGroup</t>
         </is>
       </c>
     </row>
@@ -44083,6 +45599,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD334" t="inlineStr">
+        <is>
+          <t>getChildren()</t>
+        </is>
+      </c>
+      <c r="AE334" t="inlineStr">
+        <is>
+          <t>JournalMediaGroup</t>
+        </is>
+      </c>
     </row>
     <row r="335" ht="356.5" customHeight="1">
       <c r="A335" t="n">
@@ -44151,6 +45677,21 @@
 	//UI.showAlert("ACKNOWLEDGMENT", "Saved!");
 }
 }</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>WARNING | ACKNOWLEDGMENT</t>
+        </is>
+      </c>
+      <c r="AD335" t="inlineStr">
+        <is>
+          <t>updates attributes, shows user alert</t>
+        </is>
+      </c>
+      <c r="AE335" t="inlineStr">
+        <is>
+          <t>JournalMediaGroup</t>
         </is>
       </c>
     </row>
@@ -44230,6 +45771,21 @@
 }</t>
         </is>
       </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>WARNING | ACKNOWLEDGMENT</t>
+        </is>
+      </c>
+      <c r="AD336" t="inlineStr">
+        <is>
+          <t>updates attributes, shows user alert</t>
+        </is>
+      </c>
+      <c r="AE336" t="inlineStr">
+        <is>
+          <t>JournalMediaGroup</t>
+        </is>
+      </c>
     </row>
     <row r="337" ht="409.5" customHeight="1">
       <c r="A337" t="n">
@@ -44305,6 +45861,21 @@
 	//UI.showAlert("ACKNOWLEDGMENT", "Saved!");
 }
 }</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>WARNING | ACKNOWLEDGMENT</t>
+        </is>
+      </c>
+      <c r="AD337" t="inlineStr">
+        <is>
+          <t>updates attributes, shows user alert</t>
+        </is>
+      </c>
+      <c r="AE337" t="inlineStr">
+        <is>
+          <t>JournalMediaGroup</t>
         </is>
       </c>
     </row>
@@ -44371,6 +45942,16 @@
  	}
  //}
 }</t>
+        </is>
+      </c>
+      <c r="AD338" t="inlineStr">
+        <is>
+          <t>looks up related records; updates attributes</t>
+        </is>
+      </c>
+      <c r="AE338" t="inlineStr">
+        <is>
+          <t>JournalUpsertGroup</t>
         </is>
       </c>
     </row>
@@ -44509,6 +46090,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD339" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue(), getChildren(), getParent()</t>
+        </is>
+      </c>
+      <c r="AE339" t="inlineStr">
+        <is>
+          <t>JournalUpsertGroup</t>
+        </is>
+      </c>
     </row>
     <row r="340" ht="409.5" customHeight="1">
       <c r="A340" t="n">
@@ -44606,6 +46197,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD340" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE340" t="inlineStr">
+        <is>
+          <t>JournalUpsertGroup</t>
+        </is>
+      </c>
     </row>
     <row r="341" ht="409.5" customHeight="1">
       <c r="A341" t="n">
@@ -44729,6 +46330,16 @@
 */</t>
         </is>
       </c>
+      <c r="AD341" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE341" t="inlineStr">
+        <is>
+          <t>JournalUpsertGroup</t>
+        </is>
+      </c>
     </row>
     <row r="342" ht="356.5" customHeight="1">
       <c r="A342" t="n">
@@ -44793,6 +46404,21 @@
 	genericFunctions.sendEmail(MAILHOME, emailTo, emailSubject, emailBody);
 }
 }</t>
+        </is>
+      </c>
+      <c r="AC342" t="inlineStr">
+        <is>
+          <t>GenericFunctions (genericFunctions)</t>
+        </is>
+      </c>
+      <c r="AD342" t="inlineStr">
+        <is>
+          <t>sends email notification</t>
+        </is>
+      </c>
+      <c r="AE342" t="inlineStr">
+        <is>
+          <t>JournalUpsertGroup</t>
         </is>
       </c>
     </row>
@@ -44863,6 +46489,21 @@
 }</t>
         </is>
       </c>
+      <c r="AC343" t="inlineStr">
+        <is>
+          <t>GenericFunctions (genericFunctions)</t>
+        </is>
+      </c>
+      <c r="AD343" t="inlineStr">
+        <is>
+          <t>updates attributes, sends email notification</t>
+        </is>
+      </c>
+      <c r="AE343" t="inlineStr">
+        <is>
+          <t>JournalUpsertGroup</t>
+        </is>
+      </c>
     </row>
     <row r="344" ht="93" customHeight="1">
       <c r="A344" t="n">
@@ -44910,6 +46551,16 @@
 exports.operation0 = function (node) {
 node.approve();
 }</t>
+        </is>
+      </c>
+      <c r="AD344" t="inlineStr">
+        <is>
+          <t>approves items</t>
+        </is>
+      </c>
+      <c r="AE344" t="inlineStr">
+        <is>
+          <t>JournalUpsertGroup</t>
         </is>
       </c>
     </row>
@@ -45111,6 +46762,21 @@
 }</t>
         </is>
       </c>
+      <c r="AC345" t="inlineStr">
+        <is>
+          <t>GenericFunctions (genericFunctions)</t>
+        </is>
+      </c>
+      <c r="AD345" t="inlineStr">
+        <is>
+          <t>approves items, updates attributes</t>
+        </is>
+      </c>
+      <c r="AE345" t="inlineStr">
+        <is>
+          <t>JournalUpsertGroup</t>
+        </is>
+      </c>
     </row>
     <row r="346" ht="409.5" customHeight="1">
       <c r="A346" t="n">
@@ -45388,6 +47054,16 @@
 */</t>
         </is>
       </c>
+      <c r="AD346" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE346" t="inlineStr">
+        <is>
+          <t>JournalWorkflowGroup</t>
+        </is>
+      </c>
     </row>
     <row r="347" ht="155" customHeight="1">
       <c r="A347" t="n">
@@ -45439,6 +47115,21 @@
 UI.showAlert("INFO", "Journal Successfully Created!");
 //UI.navigate("homepage",null);
 }</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>INFO: Journal Successfully Created!</t>
+        </is>
+      </c>
+      <c r="AD347" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE347" t="inlineStr">
+        <is>
+          <t>JournalWorkflowGroup</t>
         </is>
       </c>
     </row>
@@ -45576,6 +47267,21 @@
 }</t>
         </is>
       </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>WARNING: OA Revenue Subcategories Start Date must be populated on OASubcategory. Add the date to proceed. | WARNING: OA Revenue Subcategories End Date must be populated on previous OASubcategory. Add the date to proceed.</t>
+        </is>
+      </c>
+      <c r="AD348" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE348" t="inlineStr">
+        <is>
+          <t>JournalWorkflowGroup</t>
+        </is>
+      </c>
     </row>
     <row r="349" ht="409.5" customHeight="1">
       <c r="A349" t="n">
@@ -45653,6 +47359,16 @@
   "pluginType" : "Operation"
 }
 */</t>
+        </is>
+      </c>
+      <c r="AD349" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE349" t="inlineStr">
+        <is>
+          <t>JournalWorkflowGroup</t>
         </is>
       </c>
     </row>
@@ -45743,6 +47459,16 @@
 }
 return true;
 }</t>
+        </is>
+      </c>
+      <c r="AD350" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE350" t="inlineStr">
+        <is>
+          <t>JournalWorkflowGroup</t>
         </is>
       </c>
     </row>
@@ -45820,6 +47546,21 @@
 }</t>
         </is>
       </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>WARNING | ACKNOWLEDGMENT</t>
+        </is>
+      </c>
+      <c r="AD351" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE351" t="inlineStr">
+        <is>
+          <t>JournalWorkflowGroup</t>
+        </is>
+      </c>
     </row>
     <row r="352" ht="356.5" customHeight="1">
       <c r="A352" t="n">
@@ -45888,6 +47629,21 @@
 	//UI.showAlert("ACKNOWLEDGMENT", "Saved!");
 }
 }</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>WARNING | ACKNOWLEDGMENT</t>
+        </is>
+      </c>
+      <c r="AD352" t="inlineStr">
+        <is>
+          <t>updates attributes, shows user alert</t>
+        </is>
+      </c>
+      <c r="AE352" t="inlineStr">
+        <is>
+          <t>JournalWorkflowGroup</t>
         </is>
       </c>
     </row>
@@ -46004,6 +47760,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD353" t="inlineStr">
+        <is>
+          <t>approves items, updates attributes</t>
+        </is>
+      </c>
+      <c r="AE353" t="inlineStr">
+        <is>
+          <t>JournalWorkflowGroup</t>
+        </is>
+      </c>
     </row>
     <row r="354" ht="325.5" customHeight="1">
       <c r="A354" t="n">
@@ -46069,6 +47835,16 @@
 	//log.info("JournalOAOrigin" + JournalOAOrigin);
 }
 }</t>
+        </is>
+      </c>
+      <c r="AD354" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE354" t="inlineStr">
+        <is>
+          <t>JournalWorkflowGroup</t>
         </is>
       </c>
     </row>
@@ -46128,6 +47904,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD355" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE355" t="inlineStr">
+        <is>
+          <t>Libraries</t>
+        </is>
+      </c>
     </row>
     <row r="356" ht="139.5" customHeight="1">
       <c r="A356" t="n">
@@ -46183,6 +47969,16 @@
 NODE.getValue("ProductTitle").setSimpleValue(name);
 LOG.info("Austin " + name);
 }</t>
+        </is>
+      </c>
+      <c r="AD356" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE356" t="inlineStr">
+        <is>
+          <t>OtherProductCollectionRules</t>
         </is>
       </c>
     </row>
@@ -46253,6 +48049,16 @@
 */</t>
         </is>
       </c>
+      <c r="AD357" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE357" t="inlineStr">
+        <is>
+          <t>OtherProductCollectionRules</t>
+        </is>
+      </c>
     </row>
     <row r="358" ht="217" customHeight="1">
       <c r="A358" t="n">
@@ -46313,6 +48119,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD358" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE358" t="inlineStr">
+        <is>
+          <t>OtherProductCollectionRules</t>
+        </is>
+      </c>
     </row>
     <row r="359" ht="170.5" customHeight="1">
       <c r="A359" t="n">
@@ -46367,6 +48183,16 @@
 	node.getValue("CollectionStatus").setSimpleValue("Active");
 	//log.info("collType " + collType);
 }</t>
+        </is>
+      </c>
+      <c r="AD359" t="inlineStr">
+        <is>
+          <t>updates attributes</t>
+        </is>
+      </c>
+      <c r="AE359" t="inlineStr">
+        <is>
+          <t>OtherProductCollectionRules</t>
         </is>
       </c>
     </row>
@@ -46426,6 +48252,16 @@
 */</t>
         </is>
       </c>
+      <c r="AD360" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE360" t="inlineStr">
+        <is>
+          <t>OtherProductCollectionRules</t>
+        </is>
+      </c>
     </row>
     <row r="361" ht="155" customHeight="1">
       <c r="A361" t="n">
@@ -46474,6 +48310,21 @@
 var mySel = UI.getSelection();
 UI.showAlert("INFO", "Search Initiated For Other Products");
 }</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>INFO: Search Initiated For Other Products</t>
+        </is>
+      </c>
+      <c r="AD361" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE361" t="inlineStr">
+        <is>
+          <t>OtherProducts</t>
         </is>
       </c>
     </row>
@@ -46542,6 +48393,16 @@
   "pluginType" : "Operation"
 }
 */</t>
+        </is>
+      </c>
+      <c r="AD362" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE362" t="inlineStr">
+        <is>
+          <t>OtherProducts</t>
         </is>
       </c>
     </row>
@@ -46661,6 +48522,26 @@
 }</t>
         </is>
       </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>INFO: DOI/URL overridden Manually</t>
+        </is>
+      </c>
+      <c r="AC363" t="inlineStr">
+        <is>
+          <t>GenericFunctions (genericFunctions)</t>
+        </is>
+      </c>
+      <c r="AD363" t="inlineStr">
+        <is>
+          <t>updates attributes, shows user alert</t>
+        </is>
+      </c>
+      <c r="AE363" t="inlineStr">
+        <is>
+          <t>OtherProducts</t>
+        </is>
+      </c>
     </row>
     <row r="364" ht="409.5" customHeight="1">
       <c r="A364" t="n">
@@ -46759,6 +48640,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD364" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE364" t="inlineStr">
+        <is>
+          <t>OutboundIntegrationRules</t>
+        </is>
+      </c>
     </row>
     <row r="365" ht="409.5" customHeight="1">
       <c r="A365" t="n">
@@ -46836,6 +48727,16 @@
   }
 }
 }</t>
+        </is>
+      </c>
+      <c r="AD365" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE365" t="inlineStr">
+        <is>
+          <t>OutboundIntegrationRules</t>
         </is>
       </c>
     </row>
@@ -46931,6 +48832,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD366" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE366" t="inlineStr">
+        <is>
+          <t>OutboundIntegrationRules</t>
+        </is>
+      </c>
     </row>
     <row r="367" ht="409.5" customHeight="1">
       <c r="A367" t="n">
@@ -47009,6 +48920,16 @@
   }
 }
 }</t>
+        </is>
+      </c>
+      <c r="AD367" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE367" t="inlineStr">
+        <is>
+          <t>OutboundIntegrationRules</t>
         </is>
       </c>
     </row>
@@ -47104,6 +49025,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD368" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE368" t="inlineStr">
+        <is>
+          <t>OutboundIntegrationRules</t>
+        </is>
+      </c>
     </row>
     <row r="369" ht="409.5" customHeight="1">
       <c r="A369" t="n">
@@ -47182,6 +49113,16 @@
   }
 }
 }</t>
+        </is>
+      </c>
+      <c r="AD369" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE369" t="inlineStr">
+        <is>
+          <t>OutboundIntegrationRules</t>
         </is>
       </c>
     </row>
@@ -47279,6 +49220,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD370" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE370" t="inlineStr">
+        <is>
+          <t>OutboundIntegrationRules</t>
+        </is>
+      </c>
     </row>
     <row r="371" ht="409.5" customHeight="1">
       <c r="A371" t="n">
@@ -47356,6 +49307,16 @@
   }
 }
 }</t>
+        </is>
+      </c>
+      <c r="AD371" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE371" t="inlineStr">
+        <is>
+          <t>OutboundIntegrationRules</t>
         </is>
       </c>
     </row>
@@ -47452,6 +49413,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD372" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue(), getParent()</t>
+        </is>
+      </c>
+      <c r="AE372" t="inlineStr">
+        <is>
+          <t>OutboundIntegrationRules</t>
+        </is>
+      </c>
     </row>
     <row r="373" ht="263.5" customHeight="1">
       <c r="A373" t="n">
@@ -47508,6 +49479,16 @@
 //	return true;
 //}
 }</t>
+        </is>
+      </c>
+      <c r="AD373" t="inlineStr">
+        <is>
+          <t>Rule-specific processing</t>
+        </is>
+      </c>
+      <c r="AE373" t="inlineStr">
+        <is>
+          <t>OutboundIntegrationRules</t>
         </is>
       </c>
     </row>
@@ -47588,6 +49569,16 @@
 //}
 return false;
 }</t>
+        </is>
+      </c>
+      <c r="AD374" t="inlineStr">
+        <is>
+          <t>getValue(), getSimpleValue()</t>
+        </is>
+      </c>
+      <c r="AE374" t="inlineStr">
+        <is>
+          <t>OutboundIntegrationRules</t>
         </is>
       </c>
     </row>
@@ -47767,6 +49758,21 @@
 */</t>
         </is>
       </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>ERROR: There is no Multimedia for the journal. Please Check</t>
+        </is>
+      </c>
+      <c r="AD375" t="inlineStr">
+        <is>
+          <t>looks up related records; creates/updates references, updates attributes, shows user alert</t>
+        </is>
+      </c>
+      <c r="AE375" t="inlineStr">
+        <is>
+          <t>PackageGroup</t>
+        </is>
+      </c>
     </row>
     <row r="376" ht="409.5" customHeight="1">
       <c r="A376" t="n">
@@ -47836,6 +49842,21 @@
 }</t>
         </is>
       </c>
+      <c r="AC376" t="inlineStr">
+        <is>
+          <t>GenericFunctions (genericFunctions)</t>
+        </is>
+      </c>
+      <c r="AD376" t="inlineStr">
+        <is>
+          <t>updates attributes, sends email notification</t>
+        </is>
+      </c>
+      <c r="AE376" t="inlineStr">
+        <is>
+          <t>PackageGroup</t>
+        </is>
+      </c>
     </row>
     <row r="377" ht="108.5" customHeight="1">
       <c r="A377" t="n">
@@ -47884,6 +49905,21 @@
 UI.showAlert("INFO", "Publication Year Creation Process initiated.");
 UI.navigate("PublicationYearCreationScreen", NODE);
 }</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>INFO: Publication Year Creation Process initiated.</t>
+        </is>
+      </c>
+      <c r="AD377" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE377" t="inlineStr">
+        <is>
+          <t>PubYearGroup</t>
         </is>
       </c>
     </row>
@@ -47953,6 +49989,21 @@
 }</t>
         </is>
       </c>
+      <c r="AC378" t="inlineStr">
+        <is>
+          <t>PublicationYearFunctions (pubLibrary)</t>
+        </is>
+      </c>
+      <c r="AD378" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE378" t="inlineStr">
+        <is>
+          <t>PubYearGroup</t>
+        </is>
+      </c>
     </row>
     <row r="379" ht="325.5" customHeight="1">
       <c r="A379" t="n">
@@ -48018,6 +50069,21 @@
 	UI.navigate("DigitalPublicationYearScreen", year);
 }
 }</t>
+        </is>
+      </c>
+      <c r="AC379" t="inlineStr">
+        <is>
+          <t>PublicationYearFunctions (pubLibrary)</t>
+        </is>
+      </c>
+      <c r="AD379" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE379" t="inlineStr">
+        <is>
+          <t>PubYearGroup</t>
         </is>
       </c>
     </row>
@@ -48081,6 +50147,21 @@
 UI.showAlert(severity,headline,body);
 UI.navigate(screenID, year);
 }</t>
+        </is>
+      </c>
+      <c r="AC380" t="inlineStr">
+        <is>
+          <t>PublicationYearFunctions (pubLibrary)</t>
+        </is>
+      </c>
+      <c r="AD380" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE380" t="inlineStr">
+        <is>
+          <t>PubYearGroup</t>
         </is>
       </c>
     </row>
@@ -48195,6 +50276,21 @@
 }
 return "An issue already exists with this Volume and issue number";
 }</t>
+        </is>
+      </c>
+      <c r="AC381" t="inlineStr">
+        <is>
+          <t>PublicationYearFunctions (pubLibrary)</t>
+        </is>
+      </c>
+      <c r="AD381" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE381" t="inlineStr">
+        <is>
+          <t>PubYearGroup</t>
         </is>
       </c>
     </row>
@@ -48323,6 +50419,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD382" t="inlineStr">
+        <is>
+          <t>approves items, updates attributes</t>
+        </is>
+      </c>
+      <c r="AE382" t="inlineStr">
+        <is>
+          <t>PubYearGroup</t>
+        </is>
+      </c>
     </row>
     <row r="383" ht="409.5" customHeight="1">
       <c r="A383" t="n">
@@ -48409,6 +50515,16 @@
 }</t>
         </is>
       </c>
+      <c r="AD383" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE383" t="inlineStr">
+        <is>
+          <t>PubYearGroup</t>
+        </is>
+      </c>
     </row>
     <row r="384" ht="108.5" customHeight="1">
       <c r="A384" t="n">
@@ -48457,6 +50573,21 @@
 UI.showAlert("INFO", "Publication Year Creation Process initiated.");
 UI.navigate("PublicationYearCreationScreen",  UI.getSelection().get(0));
 }</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>INFO: Publication Year Creation Process initiated.</t>
+        </is>
+      </c>
+      <c r="AD384" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE384" t="inlineStr">
+        <is>
+          <t>PubYearGroup</t>
         </is>
       </c>
     </row>
@@ -48513,6 +50644,21 @@
 }</t>
         </is>
       </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>INFO: Publication Year Reannouncement Process cancelled.</t>
+        </is>
+      </c>
+      <c r="AD385" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE385" t="inlineStr">
+        <is>
+          <t>ReannouncementGroup</t>
+        </is>
+      </c>
     </row>
     <row r="386" ht="108.5" customHeight="1">
       <c r="A386" t="n">
@@ -48563,6 +50709,21 @@
 }</t>
         </is>
       </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>INFO: Publication Year Reannouncement Process initiated.</t>
+        </is>
+      </c>
+      <c r="AD386" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE386" t="inlineStr">
+        <is>
+          <t>ReannouncementGroup</t>
+        </is>
+      </c>
     </row>
     <row r="387" ht="108.5" customHeight="1">
       <c r="A387" t="n">
@@ -48611,6 +50772,21 @@
 UI.showAlert("INFO", "Volumes Reannouncement Process initiated.");
 UI.navigate("ReannouncementPubYearByVolumesSubScreen",  UI.getSelection().get(0));
 }</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>INFO: Volumes Reannouncement Process initiated.</t>
+        </is>
+      </c>
+      <c r="AD387" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE387" t="inlineStr">
+        <is>
+          <t>ReannouncementGroup</t>
         </is>
       </c>
     </row>
@@ -48674,6 +50850,16 @@
 	log.info("Error: " + e);
 }
 }</t>
+        </is>
+      </c>
+      <c r="AD388" t="inlineStr">
+        <is>
+          <t>creates/updates references</t>
+        </is>
+      </c>
+      <c r="AE388" t="inlineStr">
+        <is>
+          <t>ReferenceLinkGroup</t>
         </is>
       </c>
     </row>
@@ -48740,6 +50926,16 @@
 	log.info("Error: " + e);
 }
 }</t>
+        </is>
+      </c>
+      <c r="AD389" t="inlineStr">
+        <is>
+          <t>creates/updates references, updates attributes</t>
+        </is>
+      </c>
+      <c r="AE389" t="inlineStr">
+        <is>
+          <t>ReferenceLinkGroup</t>
         </is>
       </c>
     </row>
@@ -48981,6 +51177,21 @@
 // ... truncated ...</t>
         </is>
       </c>
+      <c r="AC390" t="inlineStr">
+        <is>
+          <t>IssueFunctions (issueLibrary), VolumeFunctions (volumeLibrary)</t>
+        </is>
+      </c>
+      <c r="AD390" t="inlineStr">
+        <is>
+          <t>updates attributes, shows user alert</t>
+        </is>
+      </c>
+      <c r="AE390" t="inlineStr">
+        <is>
+          <t>VolumesGroup</t>
+        </is>
+      </c>
     </row>
     <row r="391" ht="186" customHeight="1">
       <c r="A391" t="n">
@@ -49034,6 +51245,21 @@
 	UI.navigate("DigitalPublicationYearScreen", NODE);
 }
 }</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>INFO: Volume Creation Process cancelled.</t>
+        </is>
+      </c>
+      <c r="AD391" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE391" t="inlineStr">
+        <is>
+          <t>VolumesGroup</t>
         </is>
       </c>
     </row>
@@ -49111,6 +51337,21 @@
 	UI.navigate("DigitalPublicationYearScreen", NODE);
 }
 }</t>
+        </is>
+      </c>
+      <c r="AC392" t="inlineStr">
+        <is>
+          <t>GenericFunctions (genericFunctions), VolumeFunctions (volumeLibrary)</t>
+        </is>
+      </c>
+      <c r="AD392" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE392" t="inlineStr">
+        <is>
+          <t>VolumesGroup</t>
         </is>
       </c>
     </row>
@@ -49188,6 +51429,21 @@
 }</t>
         </is>
       </c>
+      <c r="AC393" t="inlineStr">
+        <is>
+          <t>GenericFunctions (genericFunctions), VolumeFunctions (volumeLibrary)</t>
+        </is>
+      </c>
+      <c r="AD393" t="inlineStr">
+        <is>
+          <t>updates attributes, shows user alert</t>
+        </is>
+      </c>
+      <c r="AE393" t="inlineStr">
+        <is>
+          <t>VolumesGroup</t>
+        </is>
+      </c>
     </row>
     <row r="394" ht="387.5" customHeight="1">
       <c r="A394" t="n">
@@ -49249,6 +51505,21 @@
 }
 UI.showAlert("INFO", "Volume(s) succesfully copied to the Online Journal.", "");
 }</t>
+        </is>
+      </c>
+      <c r="AC394" t="inlineStr">
+        <is>
+          <t>IssueFunctions (issueLibrary), VolumeFunctions (volumeLibrary), PublicationYearFunctions (pubLibrary)</t>
+        </is>
+      </c>
+      <c r="AD394" t="inlineStr">
+        <is>
+          <t>shows user alert</t>
+        </is>
+      </c>
+      <c r="AE394" t="inlineStr">
+        <is>
+          <t>VolumesGroup</t>
         </is>
       </c>
     </row>
@@ -49374,6 +51645,16 @@
 ui.navigate(screenID,node);
 ui.showAlert(severity,headline,'')
 }</t>
+        </is>
+      </c>
+      <c r="AD395" t="inlineStr">
+        <is>
+          <t>updates attributes, creates related objects, shows user alert</t>
+        </is>
+      </c>
+      <c r="AE395" t="inlineStr">
+        <is>
+          <t>WileyPOCRules</t>
         </is>
       </c>
     </row>
@@ -49452,36 +51733,16 @@
       <c r="J1" s="7" t="n"/>
       <c r="K1" s="7" t="n"/>
       <c r="M1" s="7" t="n"/>
-      <c r="N1" s="7" t="n"/>
-      <c r="O1" s="34" t="inlineStr">
-        <is>
-          <t>Workflow / Configuration 1</t>
-        </is>
-      </c>
+      <c r="N1" s="35" t="n"/>
+      <c r="O1" s="36" t="n"/>
       <c r="P1" s="33" t="n"/>
-      <c r="Q1" s="34" t="inlineStr">
-        <is>
-          <t>Workflow / Configuration 2</t>
-        </is>
-      </c>
+      <c r="Q1" s="33" t="n"/>
       <c r="R1" s="33" t="n"/>
-      <c r="S1" s="34" t="inlineStr">
-        <is>
-          <t>Workflow / Configuration 3</t>
-        </is>
-      </c>
+      <c r="S1" s="33" t="n"/>
       <c r="T1" s="33" t="n"/>
-      <c r="U1" s="34" t="inlineStr">
-        <is>
-          <t>Workflow / Configuration 4</t>
-        </is>
-      </c>
+      <c r="U1" s="33" t="n"/>
       <c r="V1" s="33" t="n"/>
-      <c r="W1" s="34" t="inlineStr">
-        <is>
-          <t>Workflow / Configuration 5</t>
-        </is>
-      </c>
+      <c r="W1" s="33" t="n"/>
       <c r="X1" s="33" t="n"/>
       <c r="Y1" s="7" t="n"/>
       <c r="Z1" s="7" t="n"/>

--- a/Stibo STEP Global Business Rules v1.3.with-detail.xlsx
+++ b/Stibo STEP Global Business Rules v1.3.with-detail.xlsx
@@ -31664,6 +31664,11 @@
           <t>Actions</t>
         </is>
       </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="409.5" customHeight="1">
       <c r="A201" t="n">
@@ -31913,6 +31918,11 @@
           <t>Actions</t>
         </is>
       </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="341" customHeight="1">
       <c r="A202" t="n">
@@ -31998,6 +32008,11 @@
           <t>Actions</t>
         </is>
       </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="341" customHeight="1">
       <c r="A203" t="n">
@@ -32081,6 +32096,11 @@
       <c r="AE203" t="inlineStr">
         <is>
           <t>Actions</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -32165,6 +32185,11 @@
       <c r="AE204" t="inlineStr">
         <is>
           <t>Actions</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -32291,6 +32316,11 @@
           <t>Actions</t>
         </is>
       </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="409.5" customHeight="1">
       <c r="A206" t="n">
@@ -32482,6 +32512,11 @@
           <t>Actions</t>
         </is>
       </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="409.5" customHeight="1">
       <c r="A207" t="n">
@@ -32569,6 +32604,11 @@
       <c r="AE207" t="inlineStr">
         <is>
           <t>Actions</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -32677,6 +32717,11 @@
       <c r="AE208" t="inlineStr">
         <is>
           <t>Actions</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -32764,6 +32809,11 @@
           <t>Actions</t>
         </is>
       </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="341" customHeight="1">
       <c r="A210" t="n">
@@ -32847,6 +32897,11 @@
       <c r="AE210" t="inlineStr">
         <is>
           <t>Actions</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -32977,6 +33032,11 @@
           <t>Actions</t>
         </is>
       </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="409.5" customHeight="1">
       <c r="A212" t="n">
@@ -33087,6 +33147,11 @@
       <c r="AE212" t="inlineStr">
         <is>
           <t>Actions</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -33207,6 +33272,11 @@
           <t>Actions</t>
         </is>
       </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="409.5" customHeight="1">
       <c r="A214" t="n">
@@ -33319,6 +33389,11 @@
           <t>Actions</t>
         </is>
       </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="139.5" customHeight="1">
       <c r="A215" t="n">
@@ -33384,6 +33459,11 @@
           <t>Actions</t>
         </is>
       </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="124" customHeight="1">
       <c r="A216" t="n">
@@ -33441,6 +33521,11 @@
       <c r="AE216" t="inlineStr">
         <is>
           <t>Actions</t>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -33507,6 +33592,11 @@
       <c r="AE217" t="inlineStr">
         <is>
           <t>Actions</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -33608,6 +33698,11 @@
       <c r="AE218" t="inlineStr">
         <is>
           <t>Actions</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -33822,6 +33917,11 @@
           <t>AutoClassifyRules</t>
         </is>
       </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="409.5" customHeight="1">
       <c r="A220" t="n">
@@ -33913,6 +34013,11 @@
       <c r="AE220" t="inlineStr">
         <is>
           <t>AutoClassifyRules</t>
+        </is>
+      </c>
+      <c r="AG220" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -34033,6 +34138,11 @@
       <c r="AE221" t="inlineStr">
         <is>
           <t>AutoClassifyRules</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -34298,6 +34408,11 @@
           <t>AutoClassifyRules</t>
         </is>
       </c>
+      <c r="AG222" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="409.5" customHeight="1">
       <c r="A223" t="n">
@@ -34385,6 +34500,11 @@
       <c r="AE223" t="inlineStr">
         <is>
           <t>BackfilesUpsertGroup</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -34464,6 +34584,11 @@
           <t>BackfilesUpsertGroup</t>
         </is>
       </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="372" customHeight="1">
       <c r="A225" t="n">
@@ -34548,6 +34673,11 @@
       <c r="AE225" t="inlineStr">
         <is>
           <t>BackfilesUpsertGroup</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -34668,6 +34798,11 @@
           <t>CollectionGroup</t>
         </is>
       </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="62" customHeight="1">
       <c r="A227" t="n">
@@ -34723,6 +34858,11 @@
       <c r="AE227" t="inlineStr">
         <is>
           <t>Conditions</t>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -34811,6 +34951,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="62" customHeight="1">
       <c r="A229" t="n">
@@ -34866,6 +35011,11 @@
       <c r="AE229" t="inlineStr">
         <is>
           <t>Conditions</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -34957,6 +35107,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="217" customHeight="1">
       <c r="A231" t="n">
@@ -35023,6 +35178,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG231" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="62" customHeight="1">
       <c r="A232" t="n">
@@ -35078,6 +35238,11 @@
       <c r="AE232" t="inlineStr">
         <is>
           <t>Conditions</t>
+        </is>
+      </c>
+      <c r="AG232" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -35301,6 +35466,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="409.5" customHeight="1">
       <c r="A234" t="n">
@@ -35436,6 +35606,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG234" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="232.5" customHeight="1">
       <c r="A235" t="n">
@@ -35504,6 +35679,11 @@
       <c r="AE235" t="inlineStr">
         <is>
           <t>Conditions</t>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -35600,6 +35780,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG236" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="409.5" customHeight="1">
       <c r="A237" t="n">
@@ -35689,6 +35874,11 @@
       <c r="AE237" t="inlineStr">
         <is>
           <t>Conditions</t>
+        </is>
+      </c>
+      <c r="AG237" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -35839,6 +36029,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG238" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="409.5" customHeight="1">
       <c r="A239" t="n">
@@ -36270,6 +36465,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG239" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="356.5" customHeight="1">
       <c r="A240" t="n">
@@ -36342,6 +36542,11 @@
       <c r="AE240" t="inlineStr">
         <is>
           <t>Conditions</t>
+        </is>
+      </c>
+      <c r="AG240" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -36496,6 +36701,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG241" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="294.5" customHeight="1">
       <c r="A242" t="n">
@@ -36571,6 +36781,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="201.5" customHeight="1">
       <c r="A243" t="n">
@@ -36638,6 +36853,11 @@
       <c r="AE243" t="inlineStr">
         <is>
           <t>Conditions</t>
+        </is>
+      </c>
+      <c r="AG243" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -36709,6 +36929,11 @@
       <c r="AE244" t="inlineStr">
         <is>
           <t>Conditions</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -36872,6 +37097,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="409.5" customHeight="1">
       <c r="A246" t="n">
@@ -36950,6 +37180,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="279" customHeight="1">
       <c r="A247" t="n">
@@ -37019,6 +37254,11 @@
       <c r="AE247" t="inlineStr">
         <is>
           <t>Conditions</t>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -37105,6 +37345,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="232.5" customHeight="1">
       <c r="A249" t="n">
@@ -37175,6 +37420,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="201.5" customHeight="1">
       <c r="A250" t="n">
@@ -37249,6 +37499,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="139.5" customHeight="1">
       <c r="A251" t="n">
@@ -37311,6 +37566,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="139.5" customHeight="1">
       <c r="A252" t="n">
@@ -37371,6 +37631,11 @@
       <c r="AE252" t="inlineStr">
         <is>
           <t>Conditions</t>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -37447,6 +37712,11 @@
       <c r="AE253" t="inlineStr">
         <is>
           <t>Conditions</t>
+        </is>
+      </c>
+      <c r="AG253" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -37533,6 +37803,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="232.5" customHeight="1">
       <c r="A255" t="n">
@@ -37603,6 +37878,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="139.5" customHeight="1">
       <c r="A256" t="n">
@@ -37670,6 +37950,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="139.5" customHeight="1">
       <c r="A257" t="n">
@@ -37730,6 +38015,11 @@
       <c r="AE257" t="inlineStr">
         <is>
           <t>Conditions</t>
+        </is>
+      </c>
+      <c r="AG257" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -37799,6 +38089,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG258" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="232.5" customHeight="1">
       <c r="A259" t="n">
@@ -37866,6 +38161,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG259" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="155" customHeight="1">
       <c r="A260" t="n">
@@ -37933,6 +38233,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG260" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="139.5" customHeight="1">
       <c r="A261" t="n">
@@ -38000,6 +38305,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG261" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="155" customHeight="1">
       <c r="A262" t="n">
@@ -38067,6 +38377,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG262" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="155" customHeight="1">
       <c r="A263" t="n">
@@ -38134,6 +38449,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG263" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="155" customHeight="1">
       <c r="A264" t="n">
@@ -38199,6 +38519,11 @@
       <c r="AE264" t="inlineStr">
         <is>
           <t>Conditions</t>
+        </is>
+      </c>
+      <c r="AG264" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -38281,6 +38606,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG265" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="155" customHeight="1">
       <c r="A266" t="n">
@@ -38348,6 +38678,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG266" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="139.5" customHeight="1">
       <c r="A267" t="n">
@@ -38415,6 +38750,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG267" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="170.5" customHeight="1">
       <c r="A268" t="n">
@@ -38482,6 +38822,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG268" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="139.5" customHeight="1">
       <c r="A269" t="n">
@@ -38549,6 +38894,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="139.5" customHeight="1">
       <c r="A270" t="n">
@@ -38616,6 +38966,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="155" customHeight="1">
       <c r="A271" t="n">
@@ -38683,6 +39038,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="155" customHeight="1">
       <c r="A272" t="n">
@@ -38750,6 +39110,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG272" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="139.5" customHeight="1">
       <c r="A273" t="n">
@@ -38817,6 +39182,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="155" customHeight="1">
       <c r="A274" t="n">
@@ -38884,6 +39254,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG274" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="217" customHeight="1">
       <c r="A275" t="n">
@@ -38949,6 +39324,11 @@
       <c r="AE275" t="inlineStr">
         <is>
           <t>Conditions</t>
+        </is>
+      </c>
+      <c r="AG275" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -39019,6 +39399,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG276" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="139.5" customHeight="1">
       <c r="A277" t="n">
@@ -39084,6 +39469,11 @@
       <c r="AE277" t="inlineStr">
         <is>
           <t>Conditions</t>
+        </is>
+      </c>
+      <c r="AG277" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -39160,6 +39550,11 @@
       <c r="AE278" t="inlineStr">
         <is>
           <t>Conditions</t>
+        </is>
+      </c>
+      <c r="AG278" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -39351,6 +39746,11 @@
           <t>Conditions</t>
         </is>
       </c>
+      <c r="AG279" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="403" customHeight="1">
       <c r="A280" t="n">
@@ -39419,6 +39819,11 @@
       <c r="AE280" t="inlineStr">
         <is>
           <t>Conditions</t>
+        </is>
+      </c>
+      <c r="AG280" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -39506,6 +39911,11 @@
           <t>Functions</t>
         </is>
       </c>
+      <c r="AG281" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="409.5" customHeight="1">
       <c r="A282" t="n">
@@ -39589,6 +39999,11 @@
           <t>Functions</t>
         </is>
       </c>
+      <c r="AG282" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="62" customHeight="1">
       <c r="A283" t="n">
@@ -39644,6 +40059,11 @@
       <c r="AE283" t="inlineStr">
         <is>
           <t>Functions</t>
+        </is>
+      </c>
+      <c r="AG283" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -39729,6 +40149,11 @@
           <t>Functions</t>
         </is>
       </c>
+      <c r="AG284" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="108.5" customHeight="1">
       <c r="A285" t="n">
@@ -39789,6 +40214,11 @@
           <t>Functions</t>
         </is>
       </c>
+      <c r="AG285" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="108.5" customHeight="1">
       <c r="A286" t="n">
@@ -39849,6 +40279,11 @@
           <t>Functions</t>
         </is>
       </c>
+      <c r="AG286" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="108.5" customHeight="1">
       <c r="A287" t="n">
@@ -39908,6 +40343,11 @@
           <t>Functions</t>
         </is>
       </c>
+      <c r="AG287" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="288" ht="62" customHeight="1">
       <c r="A288" t="n">
@@ -39958,6 +40398,11 @@
       <c r="AE288" t="inlineStr">
         <is>
           <t>Functions</t>
+        </is>
+      </c>
+      <c r="AG288" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -40118,6 +40563,11 @@
           <t>Integrations</t>
         </is>
       </c>
+      <c r="AG289" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="290" ht="409.5" customHeight="1">
       <c r="A290" t="n">
@@ -40287,6 +40737,11 @@
       <c r="AE290" t="inlineStr">
         <is>
           <t>Integrations</t>
+        </is>
+      </c>
+      <c r="AG290" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -40538,6 +40993,11 @@
           <t>Integrations</t>
         </is>
       </c>
+      <c r="AG291" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="409.5" customHeight="1">
       <c r="A292" t="n">
@@ -40806,6 +41266,11 @@
           <t>Integrations</t>
         </is>
       </c>
+      <c r="AG292" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="409.5" customHeight="1">
       <c r="A293" t="n">
@@ -40938,6 +41403,11 @@
           <t>Integrations</t>
         </is>
       </c>
+      <c r="AG293" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="294" ht="325.5" customHeight="1">
       <c r="A294" t="n">
@@ -41012,6 +41482,11 @@
       <c r="AE294" t="inlineStr">
         <is>
           <t>Integrations</t>
+        </is>
+      </c>
+      <c r="AG294" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -41089,6 +41564,11 @@
       <c r="AE295" t="inlineStr">
         <is>
           <t>Integrations</t>
+        </is>
+      </c>
+      <c r="AG295" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -41353,6 +41833,11 @@
           <t>Integrations</t>
         </is>
       </c>
+      <c r="AG296" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="297" ht="409.5" customHeight="1">
       <c r="A297" t="n">
@@ -41459,6 +41944,11 @@
           <t>Integrations</t>
         </is>
       </c>
+      <c r="AG297" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="298" ht="139.5" customHeight="1">
       <c r="A298" t="n">
@@ -41523,6 +42013,11 @@
       <c r="AE298" t="inlineStr">
         <is>
           <t>Integrations</t>
+        </is>
+      </c>
+      <c r="AG298" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -41841,6 +42336,11 @@
       <c r="AE299" t="inlineStr">
         <is>
           <t>Integrations</t>
+        </is>
+      </c>
+      <c r="AG299" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -42169,6 +42669,11 @@
           <t>Integrations</t>
         </is>
       </c>
+      <c r="AG300" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="301" ht="409.5" customHeight="1">
       <c r="A301" t="n">
@@ -42277,6 +42782,11 @@
           <t>Integrations</t>
         </is>
       </c>
+      <c r="AG301" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="302" ht="409.5" customHeight="1">
       <c r="A302" t="n">
@@ -42364,6 +42874,11 @@
       <c r="AE302" t="inlineStr">
         <is>
           <t>Integrations</t>
+        </is>
+      </c>
+      <c r="AG302" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -42469,6 +42984,11 @@
           <t>Integrations</t>
         </is>
       </c>
+      <c r="AG303" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="304" ht="409.5" customHeight="1">
       <c r="A304" t="n">
@@ -42557,6 +43077,11 @@
       <c r="AE304" t="inlineStr">
         <is>
           <t>Integrations</t>
+        </is>
+      </c>
+      <c r="AG304" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -42662,6 +43187,11 @@
           <t>Integrations</t>
         </is>
       </c>
+      <c r="AG305" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="306" ht="409.5" customHeight="1">
       <c r="A306" t="n">
@@ -42750,6 +43280,11 @@
       <c r="AE306" t="inlineStr">
         <is>
           <t>Integrations</t>
+        </is>
+      </c>
+      <c r="AG306" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -42857,6 +43392,11 @@
           <t>Integrations</t>
         </is>
       </c>
+      <c r="AG307" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="308" ht="409.5" customHeight="1">
       <c r="A308" t="n">
@@ -42944,6 +43484,11 @@
       <c r="AE308" t="inlineStr">
         <is>
           <t>Integrations</t>
+        </is>
+      </c>
+      <c r="AG308" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -43050,6 +43595,11 @@
           <t>Integrations</t>
         </is>
       </c>
+      <c r="AG309" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="310" ht="263.5" customHeight="1">
       <c r="A310" t="n">
@@ -43116,6 +43666,11 @@
       <c r="AE310" t="inlineStr">
         <is>
           <t>Integrations</t>
+        </is>
+      </c>
+      <c r="AG310" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -43208,6 +43763,11 @@
           <t>Integrations</t>
         </is>
       </c>
+      <c r="AG311" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="312" ht="409.5" customHeight="1">
       <c r="A312" t="n">
@@ -43290,6 +43850,11 @@
           <t>Integrations</t>
         </is>
       </c>
+      <c r="AG312" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="313" ht="409.5" customHeight="1">
       <c r="A313" t="n">
@@ -43390,6 +43955,11 @@
       <c r="AE313" t="inlineStr">
         <is>
           <t>Integrations</t>
+        </is>
+      </c>
+      <c r="AG313" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -43499,6 +44069,11 @@
           <t>Integrations</t>
         </is>
       </c>
+      <c r="AG314" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="315" ht="62" customHeight="1">
       <c r="A315" t="n">
@@ -43554,6 +44129,11 @@
       <c r="AE315" t="inlineStr">
         <is>
           <t>Integrations</t>
+        </is>
+      </c>
+      <c r="AG315" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -43644,6 +44224,11 @@
       <c r="AE316" t="inlineStr">
         <is>
           <t>Integrations</t>
+        </is>
+      </c>
+      <c r="AG316" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -43860,6 +44445,11 @@
           <t>Integrations</t>
         </is>
       </c>
+      <c r="AG317" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="318" ht="409.5" customHeight="1">
       <c r="A318" t="n">
@@ -43941,6 +44531,11 @@
           <t>Integrations</t>
         </is>
       </c>
+      <c r="AG318" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="319" ht="409.5" customHeight="1">
       <c r="A319" t="n">
@@ -44040,6 +44635,11 @@
       <c r="AE319" t="inlineStr">
         <is>
           <t>Integrations</t>
+        </is>
+      </c>
+      <c r="AG319" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -44196,6 +44796,11 @@
           <t>Integrations</t>
         </is>
       </c>
+      <c r="AG320" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="321" ht="186" customHeight="1">
       <c r="A321" t="n">
@@ -44263,6 +44868,11 @@
       <c r="AE321" t="inlineStr">
         <is>
           <t>IssuesGroup</t>
+        </is>
+      </c>
+      <c r="AG321" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -44485,6 +45095,11 @@
           <t>IssuesGroup</t>
         </is>
       </c>
+      <c r="AG322" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="323" ht="409.5" customHeight="1">
       <c r="A323" t="n">
@@ -44595,6 +45210,11 @@
           <t>IssuesGroup</t>
         </is>
       </c>
+      <c r="AG323" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="324" ht="409.5" customHeight="1">
       <c r="A324" t="n">
@@ -44684,6 +45304,11 @@
           <t>IssuesGroup</t>
         </is>
       </c>
+      <c r="AG324" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="325" ht="62" customHeight="1">
       <c r="A325" t="n">
@@ -44739,6 +45364,11 @@
       <c r="AE325" t="inlineStr">
         <is>
           <t>IssuesGroup</t>
+        </is>
+      </c>
+      <c r="AG325" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -44820,6 +45450,11 @@
       <c r="AE326" t="inlineStr">
         <is>
           <t>IssuesGroup</t>
+        </is>
+      </c>
+      <c r="AG326" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -44909,6 +45544,11 @@
           <t>JournalHistoryGroup</t>
         </is>
       </c>
+      <c r="AG327" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="328" ht="409.5" customHeight="1">
       <c r="A328" t="n">
@@ -45057,6 +45697,11 @@
           <t>JournalHistoryGroup</t>
         </is>
       </c>
+      <c r="AG328" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="329" ht="372" customHeight="1">
       <c r="A329" t="n">
@@ -45142,6 +45787,11 @@
           <t>JournalHistoryGroup</t>
         </is>
       </c>
+      <c r="AG329" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="330" ht="372" customHeight="1">
       <c r="A330" t="n">
@@ -45227,6 +45877,11 @@
           <t>JournalHistoryGroup</t>
         </is>
       </c>
+      <c r="AG330" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="331" ht="341" customHeight="1">
       <c r="A331" t="n">
@@ -45303,6 +45958,11 @@
       <c r="AE331" t="inlineStr">
         <is>
           <t>JournalMediaGroup</t>
+        </is>
+      </c>
+      <c r="AG331" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -45389,6 +46049,11 @@
           <t>JournalMediaGroup</t>
         </is>
       </c>
+      <c r="AG332" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="333" ht="409.5" customHeight="1">
       <c r="A333" t="n">
@@ -45531,6 +46196,11 @@
       <c r="AE333" t="inlineStr">
         <is>
           <t>JournalMediaGroup</t>
+        </is>
+      </c>
+      <c r="AG333" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -45609,6 +46279,11 @@
           <t>JournalMediaGroup</t>
         </is>
       </c>
+      <c r="AG334" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="335" ht="356.5" customHeight="1">
       <c r="A335" t="n">
@@ -45692,6 +46367,11 @@
       <c r="AE335" t="inlineStr">
         <is>
           <t>JournalMediaGroup</t>
+        </is>
+      </c>
+      <c r="AG335" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -45786,6 +46466,11 @@
           <t>JournalMediaGroup</t>
         </is>
       </c>
+      <c r="AG336" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="337" ht="409.5" customHeight="1">
       <c r="A337" t="n">
@@ -45876,6 +46561,11 @@
       <c r="AE337" t="inlineStr">
         <is>
           <t>JournalMediaGroup</t>
+        </is>
+      </c>
+      <c r="AG337" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -45952,6 +46642,11 @@
       <c r="AE338" t="inlineStr">
         <is>
           <t>JournalUpsertGroup</t>
+        </is>
+      </c>
+      <c r="AG338" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -46100,6 +46795,11 @@
           <t>JournalUpsertGroup</t>
         </is>
       </c>
+      <c r="AG339" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="340" ht="409.5" customHeight="1">
       <c r="A340" t="n">
@@ -46207,6 +46907,11 @@
           <t>JournalUpsertGroup</t>
         </is>
       </c>
+      <c r="AG340" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="341" ht="409.5" customHeight="1">
       <c r="A341" t="n">
@@ -46340,6 +47045,11 @@
           <t>JournalUpsertGroup</t>
         </is>
       </c>
+      <c r="AG341" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="342" ht="356.5" customHeight="1">
       <c r="A342" t="n">
@@ -46419,6 +47129,11 @@
       <c r="AE342" t="inlineStr">
         <is>
           <t>JournalUpsertGroup</t>
+        </is>
+      </c>
+      <c r="AG342" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -46504,6 +47219,11 @@
           <t>JournalUpsertGroup</t>
         </is>
       </c>
+      <c r="AG343" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="344" ht="93" customHeight="1">
       <c r="A344" t="n">
@@ -46561,6 +47281,11 @@
       <c r="AE344" t="inlineStr">
         <is>
           <t>JournalUpsertGroup</t>
+        </is>
+      </c>
+      <c r="AG344" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -46777,6 +47502,11 @@
           <t>JournalUpsertGroup</t>
         </is>
       </c>
+      <c r="AG345" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="346" ht="409.5" customHeight="1">
       <c r="A346" t="n">
@@ -47064,6 +47794,11 @@
           <t>JournalWorkflowGroup</t>
         </is>
       </c>
+      <c r="AG346" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="347" ht="155" customHeight="1">
       <c r="A347" t="n">
@@ -47130,6 +47865,11 @@
       <c r="AE347" t="inlineStr">
         <is>
           <t>JournalWorkflowGroup</t>
+        </is>
+      </c>
+      <c r="AG347" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -47282,6 +48022,11 @@
           <t>JournalWorkflowGroup</t>
         </is>
       </c>
+      <c r="AG348" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="349" ht="409.5" customHeight="1">
       <c r="A349" t="n">
@@ -47369,6 +48114,11 @@
       <c r="AE349" t="inlineStr">
         <is>
           <t>JournalWorkflowGroup</t>
+        </is>
+      </c>
+      <c r="AG349" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -47469,6 +48219,11 @@
       <c r="AE350" t="inlineStr">
         <is>
           <t>JournalWorkflowGroup</t>
+        </is>
+      </c>
+      <c r="AG350" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -47561,6 +48316,11 @@
           <t>JournalWorkflowGroup</t>
         </is>
       </c>
+      <c r="AG351" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="352" ht="356.5" customHeight="1">
       <c r="A352" t="n">
@@ -47644,6 +48404,11 @@
       <c r="AE352" t="inlineStr">
         <is>
           <t>JournalWorkflowGroup</t>
+        </is>
+      </c>
+      <c r="AG352" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -47770,6 +48535,11 @@
           <t>JournalWorkflowGroup</t>
         </is>
       </c>
+      <c r="AG353" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="354" ht="325.5" customHeight="1">
       <c r="A354" t="n">
@@ -47845,6 +48615,11 @@
       <c r="AE354" t="inlineStr">
         <is>
           <t>JournalWorkflowGroup</t>
+        </is>
+      </c>
+      <c r="AG354" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -47914,6 +48689,11 @@
           <t>Libraries</t>
         </is>
       </c>
+      <c r="AG355" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="356" ht="139.5" customHeight="1">
       <c r="A356" t="n">
@@ -47979,6 +48759,11 @@
       <c r="AE356" t="inlineStr">
         <is>
           <t>OtherProductCollectionRules</t>
+        </is>
+      </c>
+      <c r="AG356" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -48059,6 +48844,11 @@
           <t>OtherProductCollectionRules</t>
         </is>
       </c>
+      <c r="AG357" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="358" ht="217" customHeight="1">
       <c r="A358" t="n">
@@ -48129,6 +48919,11 @@
           <t>OtherProductCollectionRules</t>
         </is>
       </c>
+      <c r="AG358" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="359" ht="170.5" customHeight="1">
       <c r="A359" t="n">
@@ -48193,6 +48988,11 @@
       <c r="AE359" t="inlineStr">
         <is>
           <t>OtherProductCollectionRules</t>
+        </is>
+      </c>
+      <c r="AG359" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -48262,6 +49062,11 @@
           <t>OtherProductCollectionRules</t>
         </is>
       </c>
+      <c r="AG360" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="361" ht="155" customHeight="1">
       <c r="A361" t="n">
@@ -48325,6 +49130,11 @@
       <c r="AE361" t="inlineStr">
         <is>
           <t>OtherProducts</t>
+        </is>
+      </c>
+      <c r="AG361" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -48403,6 +49213,11 @@
       <c r="AE362" t="inlineStr">
         <is>
           <t>OtherProducts</t>
+        </is>
+      </c>
+      <c r="AG362" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -48542,6 +49357,11 @@
           <t>OtherProducts</t>
         </is>
       </c>
+      <c r="AG363" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="364" ht="409.5" customHeight="1">
       <c r="A364" t="n">
@@ -48650,6 +49470,11 @@
           <t>OutboundIntegrationRules</t>
         </is>
       </c>
+      <c r="AG364" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="365" ht="409.5" customHeight="1">
       <c r="A365" t="n">
@@ -48737,6 +49562,11 @@
       <c r="AE365" t="inlineStr">
         <is>
           <t>OutboundIntegrationRules</t>
+        </is>
+      </c>
+      <c r="AG365" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -48842,6 +49672,11 @@
           <t>OutboundIntegrationRules</t>
         </is>
       </c>
+      <c r="AG366" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="367" ht="409.5" customHeight="1">
       <c r="A367" t="n">
@@ -48930,6 +49765,11 @@
       <c r="AE367" t="inlineStr">
         <is>
           <t>OutboundIntegrationRules</t>
+        </is>
+      </c>
+      <c r="AG367" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -49035,6 +49875,11 @@
           <t>OutboundIntegrationRules</t>
         </is>
       </c>
+      <c r="AG368" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="369" ht="409.5" customHeight="1">
       <c r="A369" t="n">
@@ -49123,6 +49968,11 @@
       <c r="AE369" t="inlineStr">
         <is>
           <t>OutboundIntegrationRules</t>
+        </is>
+      </c>
+      <c r="AG369" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -49230,6 +50080,11 @@
           <t>OutboundIntegrationRules</t>
         </is>
       </c>
+      <c r="AG370" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="371" ht="409.5" customHeight="1">
       <c r="A371" t="n">
@@ -49317,6 +50172,11 @@
       <c r="AE371" t="inlineStr">
         <is>
           <t>OutboundIntegrationRules</t>
+        </is>
+      </c>
+      <c r="AG371" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -49423,6 +50283,11 @@
           <t>OutboundIntegrationRules</t>
         </is>
       </c>
+      <c r="AG372" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="373" ht="263.5" customHeight="1">
       <c r="A373" t="n">
@@ -49489,6 +50354,11 @@
       <c r="AE373" t="inlineStr">
         <is>
           <t>OutboundIntegrationRules</t>
+        </is>
+      </c>
+      <c r="AG373" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -49579,6 +50449,11 @@
       <c r="AE374" t="inlineStr">
         <is>
           <t>OutboundIntegrationRules</t>
+        </is>
+      </c>
+      <c r="AG374" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -49773,6 +50648,11 @@
           <t>PackageGroup</t>
         </is>
       </c>
+      <c r="AG375" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="376" ht="409.5" customHeight="1">
       <c r="A376" t="n">
@@ -49857,6 +50737,11 @@
           <t>PackageGroup</t>
         </is>
       </c>
+      <c r="AG376" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="377" ht="108.5" customHeight="1">
       <c r="A377" t="n">
@@ -49920,6 +50805,11 @@
       <c r="AE377" t="inlineStr">
         <is>
           <t>PubYearGroup</t>
+        </is>
+      </c>
+      <c r="AG377" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -50004,6 +50894,11 @@
           <t>PubYearGroup</t>
         </is>
       </c>
+      <c r="AG378" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="379" ht="325.5" customHeight="1">
       <c r="A379" t="n">
@@ -50084,6 +50979,11 @@
       <c r="AE379" t="inlineStr">
         <is>
           <t>PubYearGroup</t>
+        </is>
+      </c>
+      <c r="AG379" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -50162,6 +51062,11 @@
       <c r="AE380" t="inlineStr">
         <is>
           <t>PubYearGroup</t>
+        </is>
+      </c>
+      <c r="AG380" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -50291,6 +51196,11 @@
       <c r="AE381" t="inlineStr">
         <is>
           <t>PubYearGroup</t>
+        </is>
+      </c>
+      <c r="AG381" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -50429,6 +51339,11 @@
           <t>PubYearGroup</t>
         </is>
       </c>
+      <c r="AG382" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="383" ht="409.5" customHeight="1">
       <c r="A383" t="n">
@@ -50525,6 +51440,11 @@
           <t>PubYearGroup</t>
         </is>
       </c>
+      <c r="AG383" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
     </row>
     <row r="384" ht="108.5" customHeight="1">
       <c r="A384" t="n">
@@ -50588,6 +51508,11 @@
       <c r="AE384" t="inlineStr">
         <is>
           <t>PubYearGroup</t>
+        </is>
+      </c>
+      <c r="AG384" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -50659,6 +51584,11 @@
           <t>ReannouncementGroup</t>
         </is>
       </c>
+      <c r="AG385" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="386" ht="108.5" customHeight="1">
       <c r="A386" t="n">
@@ -50724,6 +51654,11 @@
           <t>ReannouncementGroup</t>
         </is>
       </c>
+      <c r="AG386" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="387" ht="108.5" customHeight="1">
       <c r="A387" t="n">
@@ -50787,6 +51722,11 @@
       <c r="AE387" t="inlineStr">
         <is>
           <t>ReannouncementGroup</t>
+        </is>
+      </c>
+      <c r="AG387" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -50860,6 +51800,11 @@
       <c r="AE388" t="inlineStr">
         <is>
           <t>ReferenceLinkGroup</t>
+        </is>
+      </c>
+      <c r="AG388" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -50936,6 +51881,11 @@
       <c r="AE389" t="inlineStr">
         <is>
           <t>ReferenceLinkGroup</t>
+        </is>
+      </c>
+      <c r="AG389" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -51192,6 +52142,11 @@
           <t>VolumesGroup</t>
         </is>
       </c>
+      <c r="AG390" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="391" ht="186" customHeight="1">
       <c r="A391" t="n">
@@ -51260,6 +52215,11 @@
       <c r="AE391" t="inlineStr">
         <is>
           <t>VolumesGroup</t>
+        </is>
+      </c>
+      <c r="AG391" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -51352,6 +52312,11 @@
       <c r="AE392" t="inlineStr">
         <is>
           <t>VolumesGroup</t>
+        </is>
+      </c>
+      <c r="AG392" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -51444,6 +52409,11 @@
           <t>VolumesGroup</t>
         </is>
       </c>
+      <c r="AG393" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="394" ht="387.5" customHeight="1">
       <c r="A394" t="n">
@@ -51520,6 +52490,11 @@
       <c r="AE394" t="inlineStr">
         <is>
           <t>VolumesGroup</t>
+        </is>
+      </c>
+      <c r="AG394" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -51655,6 +52630,11 @@
       <c r="AE395" t="inlineStr">
         <is>
           <t>WileyPOCRules</t>
+        </is>
+      </c>
+      <c r="AG395" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
